--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,17 +121,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -847,10 +849,10 @@
           <t>Vacant</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
       <c r="K11" s="9">
         <f>IFERROR(J11/E11,"")</f>
         <v/>
@@ -2377,7 +2379,7 @@
           <t>Occupied</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -2385,7 +2387,7 @@
       <c r="H46" s="8" t="n">
         <v>46031</v>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="I46" s="10" t="n"/>
       <c r="J46" s="7" t="n">
         <v>1575</v>
       </c>
@@ -3695,10 +3697,10 @@
           <t>Vacant</t>
         </is>
       </c>
-      <c r="G76" s="8" t="n"/>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="7" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
       <c r="K76" s="9">
         <f>IFERROR(J76/E76,"")</f>
         <v/>
@@ -5885,10 +5887,10 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="G126" s="8" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="7" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="n"/>
+      <c r="I126" s="10" t="n"/>
+      <c r="J126" s="10" t="n"/>
       <c r="K126" s="9">
         <f>IFERROR(J126/E126,"")</f>
         <v/>
@@ -8550,13 +8552,13 @@
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Knobs</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -8567,7 +8569,7 @@
       <c r="B6" s="8" t="n">
         <v>46203</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Every window below is measured from this date, never from today.</t>
         </is>
@@ -8582,7 +8584,7 @@
       <c r="B7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>How far back a lease counts as recent.</t>
         </is>
@@ -8597,7 +8599,7 @@
       <c r="B8" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>How far lease start may sit from move-in before a lease stops counting as a new tenant.</t>
         </is>
@@ -8677,23 +8679,23 @@
       <c r="C11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$E$6:$E$185),"")</f>
         <v/>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="7">
         <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A11)</f>
         <v/>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
         <v/>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="7">
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
@@ -8724,23 +8726,23 @@
       <c r="C12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$E$6:$E$185),"")</f>
         <v/>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="7">
         <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A12)</f>
         <v/>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
         <v/>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="7">
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
@@ -8771,23 +8773,23 @@
       <c r="C13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$E$6:$E$185),"")</f>
         <v/>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A13)</f>
         <v/>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
         <v/>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
         <v/>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="7">
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
@@ -8818,23 +8820,23 @@
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$E$6:$E$185),"")</f>
         <v/>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A14)</f>
         <v/>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
         <v/>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
         <v/>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
@@ -8865,23 +8867,23 @@
       <c r="C15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="7">
         <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$E$6:$E$185),"")</f>
         <v/>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A15)</f>
         <v/>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
         <v/>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="7">
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
@@ -8912,27 +8914,27 @@
       <c r="C16" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="7">
         <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$E$6:$E$185),"")</f>
         <v/>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="7">
         <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A16)</f>
         <v/>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
         <v/>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="7">
         <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
         <v/>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="7">
         <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
-      <c r="I16" s="7" t="n"/>
+      <c r="I16" s="10" t="n"/>
       <c r="J16" s="7" t="n">
         <v>0</v>
       </c>
@@ -8946,43 +8948,43 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Total / weighted</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr"/>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="13">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="15">
         <f>IFERROR(SUMPRODUCT($E$11:$E$16,$D$11:$D$16)/SUM($E$11:$E$16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="15">
         <f>SUM(E11:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="15">
         <f>SUM(F11:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="15">
         <f>SUM(G11:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="15">
         <f>IFERROR(SUMPRODUCT($F$11:$F$16,$H$11:$H$16)/SUM($F$11:$F$16),"")</f>
         <v/>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="13">
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="15">
         <f>SUM(J11:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="15">
         <f>IFERROR(SUMPRODUCT($E$11:$E$16,$K$11:$K$16)/SUM($E$11:$E$16),"")</f>
         <v/>
       </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>In-place weighted by occupied units; market rent weighted by total units.</t>
         </is>
@@ -9003,13 +9005,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Occupancy and vacancy</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -9017,7 +9019,7 @@
           <t>Total units</t>
         </is>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <f>E17</f>
         <v/>
       </c>
@@ -9028,7 +9030,7 @@
           <t>Occupied units</t>
         </is>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <f>F17</f>
         <v/>
       </c>
@@ -9039,7 +9041,7 @@
           <t>Vacant units</t>
         </is>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <f>G17</f>
         <v/>
       </c>
@@ -9050,11 +9052,11 @@
           <t>Non-revenue units</t>
         </is>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="7">
         <f>B23-B24-B25</f>
         <v/>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Models and down units: in the stock, not in either occupancy bucket.</t>
         </is>
@@ -9066,7 +9068,7 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="16">
         <f>IFERROR(B24/B23,"")</f>
         <v/>
       </c>
@@ -9077,11 +9079,11 @@
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="16">
         <f>IFERROR(1-B24/B23,"")</f>
         <v/>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>The physical-vacancy input a model consumes.</t>
         </is>
@@ -9093,7 +9095,7 @@
           <t>Weighted average in-place rent</t>
         </is>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="7">
         <f>H17</f>
         <v/>
       </c>
@@ -9104,7 +9106,7 @@
           <t>Weighted average market rent for model</t>
         </is>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <f>K17</f>
         <v/>
       </c>
@@ -9118,7 +9120,7 @@
       <c r="B32" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Counted by move-in date over the trailing 12 months.</t>
         </is>
@@ -9130,10 +9132,10 @@
           <t>Annualized turnover</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Move-ins in the window, annualized against unit count.</t>
         </is>
@@ -9257,22 +9259,22 @@
       <c r="D6" s="7" t="n">
         <v>1812</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <f>IFERROR(D6-C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="16">
         <f>IFERROR((D6-C6)/C6,"")</f>
         <v/>
       </c>
       <c r="G6" s="7" t="n">
         <v>1774</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <f>IFERROR(G6-C6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="16">
         <f>IFERROR((G6-C6)/C6,"")</f>
         <v/>
       </c>
@@ -9292,22 +9294,22 @@
       <c r="D7" s="7" t="n">
         <v>1745</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <f>IFERROR(D7-C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="16">
         <f>IFERROR((D7-C7)/C7,"")</f>
         <v/>
       </c>
       <c r="G7" s="7" t="n">
         <v>1745</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="7">
         <f>IFERROR(G7-C7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="16">
         <f>IFERROR((G7-C7)/C7,"")</f>
         <v/>
       </c>
@@ -9327,22 +9329,22 @@
       <c r="D8" s="7" t="n">
         <v>1836</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <f>IFERROR(D8-C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="16">
         <f>IFERROR((D8-C8)/C8,"")</f>
         <v/>
       </c>
       <c r="G8" s="7" t="n">
         <v>1790</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <f>IFERROR(G8-C8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="16">
         <f>IFERROR((G8-C8)/C8,"")</f>
         <v/>
       </c>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Rent Roll" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Unit Mix Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Lease Trade-Out" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Audit Trail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +59,10 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -73,12 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00595959"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,14 +132,27 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -209,6 +227,294 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Units by floor plan</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Unit Mix Summary'!D8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Unit Mix Summary'!$B$9:$B$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Unit Mix Summary'!$D$9:$D$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Units</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>In-place vs new-lease vs market rent for model</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Unit Mix Summary'!E8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Unit Mix Summary'!$B$9:$B$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Unit Mix Summary'!$E$9:$E$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Unit Mix Summary'!F8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Unit Mix Summary'!$B$9:$B$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Unit Mix Summary'!$F$9:$F$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Unit Mix Summary'!H8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Unit Mix Summary'!$B$9:$B$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Unit Mix Summary'!$H$9:$H$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Rent</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8503,21 +8809,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8554,595 +8857,507 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Knobs</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
+          <t>Months lookback</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>As-of date</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>New-tenant tol (days)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>As-of date</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>46203</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Every window below is measured from this date, never from today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Lookback months</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>How far back a lease counts as recent.</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Every window below is measured from the as-of date, never from today — a summary that silently re-windows when reopened next quarter is worse than none.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>New-tenant tolerance (days)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant.</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Floor plan</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Avg SF</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Unit count</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>In-place rent</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NEW LEASE rent</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>New #</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Market rent for model</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$B9,'Rent Roll'!$E$6:$E$185),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="7">
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$B9,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1510.818181818182</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1510.818181818182</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>New leases (n=11)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Floor plan</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Beds</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Baths</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Avg SF</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Occupied</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Avg in-place rent</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>New-lease rent</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>New-lease count</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Market rent for model</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>Basis</t>
+      <c r="A10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$B10,'Rent Roll'!$E$6:$E$185),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="7">
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$B10,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1583.285714285714</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1583.285714285714</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>New leases (n=7)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>1</v>
+      <c r="A11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$B11,'Rent Roll'!$E$6:$E$185),"")</f>
+        <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$E$6:$E$185),"")</f>
+        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$B11)</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
-        <v/>
-      </c>
-      <c r="G11" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="H11" s="7">
-        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A11,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>1510.818181818182</v>
-      </c>
-      <c r="J11" s="7" t="n">
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$B11,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1831.909090909091</v>
+      </c>
+      <c r="G11" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="K11" s="7" t="n">
-        <v>1510.818181818182</v>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="H11" s="7" t="n">
+        <v>1831.909090909091</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>New leases (n=11)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>1</v>
+      <c r="A12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C12" s="7">
+        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$B12,'Rent Roll'!$E$6:$E$185),"")</f>
+        <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$E$6:$E$185),"")</f>
+        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$B12)</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
-        <v/>
-      </c>
-      <c r="G12" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="H12" s="7">
-        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A12,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1583.285714285714</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>1583.285714285714</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=7)</t>
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$B12,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>1913</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>1913</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>New leases (n=9)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>2</v>
+      <c r="A13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$B13,'Rent Roll'!$E$6:$E$185),"")</f>
+        <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$E$6:$E$185),"")</f>
+        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$B13)</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
-        <v/>
-      </c>
-      <c r="G13" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="H13" s="7">
-        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A13,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>1831.909090909091</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>1831.909090909091</v>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=11)</t>
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$B13,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2156.5</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>2156.5</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>New leases (n=6)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>2</v>
+      <c r="A14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Cypress TH</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
+        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$B14,'Rent Roll'!$E$6:$E$185),"")</f>
+        <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$E$6:$E$185),"")</f>
+        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$B14)</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
-        <v/>
-      </c>
-      <c r="G14" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="H14" s="7">
-        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A14,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="7">
-        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$E$6:$E$185),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="7">
-        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
-        <v/>
-      </c>
-      <c r="G15" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="H15" s="7">
-        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A15,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>2156.5</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>2156.5</v>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=6)</t>
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$B14,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>2334.5</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>In-place — no new leases in window</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Cypress TH</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D16" s="7">
-        <f>IFERROR(AVERAGEIF('Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$E$6:$E$185),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="7">
-        <f>COUNTIF('Rent Roll'!$B$6:$B$185,$A16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$F$6:$F$185,"Occupied")</f>
-        <v/>
-      </c>
-      <c r="G16" s="7">
-        <f>COUNTIFS('Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$F$6:$F$185,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="H16" s="7">
-        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$B$6:$B$185,$A16,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="10" t="n"/>
-      <c r="J16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>2334.5</v>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>In-place — no new leases in window</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Total / weighted</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15">
-        <f>IFERROR(SUMPRODUCT($E$11:$E$16,$D$11:$D$16)/SUM($E$11:$E$16),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="15">
-        <f>SUM(E11:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="15">
-        <f>SUM(F11:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="15">
-        <f>SUM(G11:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="15">
-        <f>IFERROR(SUMPRODUCT($F$11:$F$16,$H$11:$H$16)/SUM($F$11:$F$16),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="15">
-        <f>SUM(J11:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="15">
-        <f>IFERROR(SUMPRODUCT($E$11:$E$16,$K$11:$K$16)/SUM($E$11:$E$16),"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>In-place weighted by occupied units; market rent weighted by total units.</t>
-        </is>
-      </c>
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C16" s="16">
+        <f>IFERROR(SUMPRODUCT($D$9:$D$14,$C$9:$C$14)/SUM($D$9:$D$14),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>SUM(D9:D14)</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>IFERROR(SUMPRODUCT($D$9:$D$14,$E$9:$E$14)/SUM($D$9:$D$14),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="16">
+        <f>SUM(G9:G14)</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IFERROR(SUMPRODUCT($D$9:$D$14,$H$9:$H$14)/SUM($D$9:$D$14),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>Weighted by unit count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Occupancy &amp; vacancy</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Market rent for model is the new-lease average where the plan has new leases inside the lookback window, and the in-place average otherwise — the Basis column says which. There is no blend of new and renewal rents anywhere in this output: a blended average is a renewal average wearing a new-lease label, and it understates trade-out on every deal it touches.</t>
-        </is>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>D16</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>New-lease rent, its count, and market rent for model are values rather than formulas on purpose: they depend on the window above, and a formula would re-window itself the day this file is reopened.</t>
-        </is>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Occupied units</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Vacant units</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Occupancy and vacancy</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Non-revenue units</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Models and down units: in the stock, in neither occupancy bucket.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="B23" s="7">
-        <f>E17</f>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B23" s="19">
+        <f>IFERROR(B20/B19,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Occupied units</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Vacant units</t>
-        </is>
-      </c>
-      <c r="B25" s="7">
-        <f>G17</f>
-        <v/>
+          <t>Vacancy</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>IFERROR(1-B20/B19,"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>The physical-vacancy input a model consumes.</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Non-revenue units</t>
-        </is>
-      </c>
-      <c r="B26" s="7">
-        <f>B23-B24-B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Models and down units: in the stock, not in either occupancy bucket.</t>
-        </is>
-      </c>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Annualised turnover rate</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="B27" s="16">
-        <f>IFERROR(B24/B23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Vacancy</t>
-        </is>
-      </c>
-      <c r="B28" s="16">
-        <f>IFERROR(1-B24/B23,"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>The physical-vacancy input a model consumes.</t>
+          <t>Annualised turnover</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Move-ins in the trailing 12 months, annualised against unit count.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Weighted average in-place rent</t>
-        </is>
-      </c>
-      <c r="B29" s="7">
-        <f>H17</f>
-        <v/>
-      </c>
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>New move-ins</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Weighted average market rent for model</t>
-        </is>
-      </c>
-      <c r="B30" s="7">
-        <f>K17</f>
-        <v/>
+          <t>Move-ins in window</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Counted by MOVE-IN date, never by lease start — a renewal stamps a fresh lease start against a resident who moved in years ago.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Window (months)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Move-ins in window</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Counted by move-in date over the trailing 12 months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Annualized turnover</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n">
+          <t>Share of units</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Move-ins in the window, annualized against unit count.</t>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Market rent for model is the new-lease average where the plan has new leases inside the lookback window, and the in-place average otherwise — the Basis column says which, per plan. No column on this tab blends lease types, and none of them claims a renewal rent: a roll cannot measure one. A blended "recently leased" average is a renewal average wearing a market-rent label, and on a stabilised property renewals outnumber new leases roughly three to two over twelve months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>New-lease rent, its count and market rent for model are values rather than formulas on purpose: they depend on the window above, and a formula would re-window itself the day this file is reopened. Unit count, average SF and in-place rent are live formulas over the Rent Roll tab.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9263,7 +9478,7 @@
         <f>IFERROR(D6-C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="19">
         <f>IFERROR((D6-C6)/C6,"")</f>
         <v/>
       </c>
@@ -9274,7 +9489,7 @@
         <f>IFERROR(G6-C6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="19">
         <f>IFERROR((G6-C6)/C6,"")</f>
         <v/>
       </c>
@@ -9298,7 +9513,7 @@
         <f>IFERROR(D7-C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="19">
         <f>IFERROR((D7-C7)/C7,"")</f>
         <v/>
       </c>
@@ -9309,7 +9524,7 @@
         <f>IFERROR(G7-C7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="19">
         <f>IFERROR((G7-C7)/C7,"")</f>
         <v/>
       </c>
@@ -9333,7 +9548,7 @@
         <f>IFERROR(D8-C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="19">
         <f>IFERROR((D8-C8)/C8,"")</f>
         <v/>
       </c>
@@ -9344,7 +9559,7 @@
         <f>IFERROR(G8-C8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="19">
         <f>IFERROR((G8-C8)/C8,"")</f>
         <v/>
       </c>
@@ -9354,6 +9569,345 @@
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A first-generation lease has no prior rent, so its percentage change is undefined and reads blank rather than as a number divided by zero.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Audit trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fixture Park — as of 2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>The rent roll, unit mix and trade-out. Every value below names the document it came from and where in it. A derived value names the values it was built from — one that could not would not have passed validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Stamped values in this workbook</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Coverage of the required set</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>42/42 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Source document</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Where in it</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Built from</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Supporting quote / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>rent_roll.as_of</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll!A2</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>rent_roll.lookback_months</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Analysis knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>rent_roll.new_tenant_tolerance_days</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>Analysis knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll!A4:K183</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>summary.in_place_rent_avg</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Unit Mix Summary!H</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Occupied units, weighted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>summary.market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Unit Mix Summary!K</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll!A:A</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Distinct unit identifiers on the roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic lease trade-out report</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Cohort averages.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -9164,7 +9164,7 @@
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>IFERROR(SUMPRODUCT($D$9:$D$14,$E$9:$E$14)/SUM($D$9:$D$14),"")</f>
+        <f>IFERROR(AVERAGEIFS('Rent Roll'!$J$6:$J$185,'Rent Roll'!$F$6:$F$185,"Occupied"),"")</f>
         <v/>
       </c>
       <c r="F16" s="14" t="n"/>
@@ -9587,11 +9587,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9643,7 +9644,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>42/42 (100%)</t>
+          <t>50/50 (100%)</t>
         </is>
       </c>
     </row>
@@ -9655,25 +9656,30 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>Value as published</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
           <t>Source document</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Where in it</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>How</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Built from</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Supporting quote / note</t>
         </is>
@@ -9687,21 +9693,26 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Rent Roll!A2</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="22" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="22" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -9711,21 +9722,26 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>Analysis knob.</t>
         </is>
@@ -9739,21 +9755,26 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Analysis knob.</t>
         </is>
@@ -9767,21 +9788,26 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>180 entries</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Rent Roll!A4:K183</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>Unit identifiers only; the source's resident-name column is never read.</t>
         </is>
@@ -9795,27 +9821,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
+          <t>1,795.36</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Unit Mix Summary!H</t>
-        </is>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>Unit Mix Summary!E</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>computed</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>rent_roll.units</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>Occupied units, weighted.</t>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Occupied units, straight off the roll.</t>
         </is>
       </c>
     </row>
@@ -9827,25 +9858,30 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>1,834.78</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Unit Mix Summary!K</t>
-        </is>
-      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>Unit Mix Summary!H</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>computed</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>rent_roll.units</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
         </is>
@@ -9859,25 +9895,30 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Rent Roll!A:A</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>rent_roll.units</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>Distinct unit identifiers on the roll.</t>
         </is>
@@ -9891,21 +9932,26 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>3 entries</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t>Synthetic lease trade-out report</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>Cohort averages.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-rent-roll-analysis.xlsx
@@ -9644,7 +9644,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50/50 (100%)</t>
+          <t>52/52 (100%)</t>
         </is>
       </c>
     </row>
